--- a/tame_output/ON/bt/strategyON_20231014.xlsx
+++ b/tame_output/ON/bt/strategyON_20231014.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -748,26 +748,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.1%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.7%</t>
+          <t>130.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1749"/>
+  <dimension ref="A1:G1750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41737,7 +41737,7 @@
         <v>45211</v>
       </c>
       <c r="B1749" t="n">
-        <v>2.801533654545558</v>
+        <v>2.800919062338662</v>
       </c>
       <c r="C1749" t="n">
         <v>2.941291882277773</v>
@@ -41753,6 +41753,29 @@
       </c>
       <c r="G1749" t="n">
         <v>4.23633102108523</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="2" t="n">
+        <v>45212</v>
+      </c>
+      <c r="B1750" t="n">
+        <v>2.806683821769451</v>
+      </c>
+      <c r="C1750" t="n">
+        <v>2.950500122107244</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>1.562399098977519</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>3.575103337384505</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>2.162447412696398</v>
+      </c>
+      <c r="G1750" t="n">
+        <v>4.247968569725085</v>
       </c>
     </row>
   </sheetData>
